--- a/src/files/archivo_actualizado_geOperarioGeneral.xlsx
+++ b/src/files/archivo_actualizado_geOperarioGeneral.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t xml:space="preserve">GUÍA DE ENTRENAMIENTO </t>
   </si>
@@ -42,16 +42,16 @@
     <t xml:space="preserve"> ÁREA</t>
   </si>
   <si>
-    <t>ADALBERTO JOSE MOYA NARVAEZ</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
+    <t>AGUILAR CAMACHO YURITZY AMEYALIN</t>
+  </si>
+  <si>
+    <t>2026-02-11</t>
   </si>
   <si>
     <t>Operario General</t>
   </si>
   <si>
-    <t>PRODUCCION</t>
+    <t>Producción</t>
   </si>
   <si>
     <t>TEMA</t>
@@ -75,37 +75,25 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Limpieza y Sanitización</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>TORRES RODRIGUEZ DANIELA</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>21 =&gt; 2</t>
-  </si>
-  <si>
-    <t>Defectología</t>
-  </si>
-  <si>
-    <t>PEREA MARCOS JOYCELYNN ANGIE</t>
+    <t>Generalidades de Control de Calidad</t>
+  </si>
+  <si>
+    <t>ANGELES MURCIA ANGEL CESAR / TORRES RODRIGUEZ DANIELA</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Buenas Practicas de Documentación</t>
-  </si>
-  <si>
-    <t>MELENDEZ CRISTOBAL GONZALO</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>Manejo de Residuos</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ SAUZA DIEGO</t>
+  </si>
+  <si>
+    <t>Aprobado</t>
   </si>
   <si>
     <t>1 DE 2</t>
@@ -846,12 +834,12 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1190625" cy="704850"/>
+    <xdr:ext cx="952500" cy="285750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -867,6 +855,201 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="952500" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1143000" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1143000" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1143000" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1190625" cy="704850"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1318,7 +1501,7 @@
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="39" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" ht="38.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>11</v>
       </c>
@@ -1343,76 +1526,64 @@
       </c>
       <c r="I5" s="28"/>
     </row>
-    <row r="6" ht="27.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" ht="51" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D6" s="32">
         <v>1</v>
       </c>
       <c r="E6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>21</v>
       </c>
       <c r="G6" s="33"/>
       <c r="H6" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="34"/>
+    </row>
+    <row r="7" ht="54.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>22</v>
-      </c>
-      <c r="I6" s="34"/>
-    </row>
-    <row r="7" ht="78" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>23</v>
       </c>
       <c r="B7" s="36"/>
       <c r="C7" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>21</v>
       </c>
       <c r="G7" s="33"/>
       <c r="H7" s="21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I7" s="34"/>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>26</v>
-      </c>
+    <row r="8" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
       <c r="B8" s="38"/>
-      <c r="C8" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="33">
-        <v>1</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>28</v>
-      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="32"/>
       <c r="G8" s="32"/>
-      <c r="H8" s="21" t="s">
-        <v>25</v>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="34"/>
     </row>
-    <row r="9" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" ht="60.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
       <c r="B9" s="38"/>
       <c r="C9" s="31"/>
@@ -1423,7 +1594,7 @@
       <c r="H9" s="21"/>
       <c r="I9" s="34"/>
     </row>
-    <row r="10" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" ht="61.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="38"/>
       <c r="C10" s="31"/>
@@ -1434,7 +1605,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="34"/>
     </row>
-    <row r="11" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" ht="56.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="35"/>
       <c r="B11" s="36"/>
       <c r="C11" s="31"/>
@@ -1489,7 +1660,7 @@
       <c r="H15" s="21"/>
       <c r="I15" s="34"/>
     </row>
-    <row r="16" ht="34.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" ht="41.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="35"/>
       <c r="B16" s="36"/>
       <c r="C16" s="31"/>
@@ -1511,7 +1682,7 @@
       <c r="H17" s="21"/>
       <c r="I17" s="34"/>
     </row>
-    <row r="18" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" ht="57.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
       <c r="B18" s="36"/>
       <c r="C18" s="31"/>
@@ -1579,7 +1750,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -1592,14 +1763,14 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
       <c r="E25" s="11"/>
       <c r="F25" s="47">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G25" s="48"/>
       <c r="H25" s="48"/>
@@ -1607,7 +1778,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B26" s="51"/>
       <c r="C26" s="51"/>
@@ -1620,7 +1791,7 @@
     </row>
     <row r="27" ht="24.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="53" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B27" s="54"/>
       <c r="C27" s="54"/>
@@ -1671,13 +1842,13 @@
       <c r="B31" s="68"/>
       <c r="C31" s="69"/>
       <c r="D31" s="68" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E31" s="68"/>
       <c r="F31" s="68"/>
       <c r="G31" s="69"/>
       <c r="H31" s="70" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I31" s="71"/>
     </row>
@@ -1687,7 +1858,7 @@
       <c r="C32" s="73"/>
       <c r="D32" s="73"/>
       <c r="E32" s="64" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F32" s="73"/>
       <c r="G32" s="73"/>

--- a/src/files/archivo_actualizado_geOperarioGeneral.xlsx
+++ b/src/files/archivo_actualizado_geOperarioGeneral.xlsx
@@ -42,16 +42,16 @@
     <t xml:space="preserve"> ÁREA</t>
   </si>
   <si>
-    <t>AGUILAR CAMACHO YURITZY AMEYALIN</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
+    <t>1042443590 - ADANY LUZ REYES RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
   </si>
   <si>
     <t>Operario General</t>
   </si>
   <si>
-    <t>Producción</t>
+    <t>PRODUCCION</t>
   </si>
   <si>
     <t>TEMA</t>
@@ -75,25 +75,25 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Generalidades de Control de Calidad</t>
-  </si>
-  <si>
-    <t>ANGELES MURCIA ANGEL CESAR / TORRES RODRIGUEZ DANIELA</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>Limpieza y Sanitización.</t>
+  </si>
+  <si>
+    <t>Daniela Parodi / Maria Alonso Ayala</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Manejo de Residuos</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ SAUZA DIEGO</t>
-  </si>
-  <si>
-    <t>Aprobado</t>
+    <t>Proceso Fabricación del jabón líquido/Solido/Hidroalcohólico Interactivo</t>
+  </si>
+  <si>
+    <t>Maria Alonso Ayala</t>
+  </si>
+  <si>
+    <t>Reprobado</t>
   </si>
   <si>
     <t>1 DE 2</t>
@@ -1558,7 +1558,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="32">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>23</v>
@@ -1770,7 +1770,7 @@
       <c r="D25" s="46"/>
       <c r="E25" s="11"/>
       <c r="F25" s="47">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G25" s="48"/>
       <c r="H25" s="48"/>
